--- a/outputs/Condom�nio_Edif�cio_Dourados_000000_seens.xlsx
+++ b/outputs/Condom�nio_Edif�cio_Dourados_000000_seens.xlsx
@@ -72,9 +72,9 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A5:L32"/>
+  <dimension ref="A5:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="3" max="3"/>
@@ -474,206 +474,708 @@
     <row r="11">
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>TOTAL RECEITAS DO MÊS</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>33637.54</v>
+          <t>(+) RECEITAS</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL DESPESAS DO MÊS</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="n">
-        <v>520613.18</v>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>TAXA DE CONDOMNIO - REF: 02/26 16.713,53</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>16713.53</v>
       </c>
     </row>
     <row r="13">
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>RESUMO DO MÊS</t>
-        </is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>16713.53</v>
       </c>
     </row>
     <row r="14">
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>RECEITAS</t>
-        </is>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>33637.54</v>
+      <c r="C14" s="1" t="inlineStr">
+        <is>
+          <t>(+) RECEITAS EXTRAS</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>DESPESAS</t>
-        </is>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>520613.18</v>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>RENDIMENTO FINANCEIRO - FUNDO DE RESERVA - REF: 02/26 62,69</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>62.69</v>
       </c>
     </row>
     <row r="16">
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL (RECEITAS - DESPESAS)</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>-486975.64</v>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>RENDIMENTO FINANCEIRO - FUNDO DE RH - REF: 02/26 42,55</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>42.55</v>
       </c>
     </row>
     <row r="17">
       <c r="C17" s="1" t="inlineStr">
         <is>
-          <t>RESUMO DAS CONTAS - POSIÇÃO CONSOLIDADA DA CONTA PESSOA JURÍDICA - SICREDI</t>
-        </is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>105.24</v>
       </c>
     </row>
     <row r="18">
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>FUNDO DE OBRA</t>
+          <t>(-) DESPESA COM PESSOAL</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>SALDO ANTERIOR</t>
-        </is>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>0</v>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>SALRIOS - MARIA GENILDA J BORGES 01/2026 03/02/2026 PIX 731,00</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>731</v>
       </c>
     </row>
     <row r="20">
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>ENTRADAS</t>
-        </is>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>0</v>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>FGTS - CEF 01/2026 19/02/2026 PIX 105,55</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>105.55</v>
       </c>
     </row>
     <row r="21">
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>SAÍDAS</t>
-        </is>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>0</v>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>DARF - RECEITA FEDERAL - PIS (8301) 01/2026 19/02/2026 GUIA 456,64</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>456.64</v>
       </c>
     </row>
     <row r="22">
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>SALDO ATUAL</t>
-        </is>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>0</v>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>ASSIST. MDICA - SECOVIMED 01/2026 06/02/2026 BOLETO 169,09</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>169.09</v>
       </c>
     </row>
     <row r="23">
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>FUNDO DE RESERVA DE POUPANÇA PERMANENTE</t>
-        </is>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>03/2026 23/02/2026 BOLETO 22,00</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="24">
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>SALDO ANTERIOR</t>
-        </is>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>0</v>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>VALE TRANSPORTE - METROCARD 03/2026 23/02/2026 BOLETO 272,69</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>272.69</v>
       </c>
     </row>
     <row r="25">
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>ENTRADAS</t>
-        </is>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>0</v>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>CESTA BSICA - VR BENEFICIOS 03/2026 23/02/2026 BOLETO 650,00</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>650</v>
       </c>
     </row>
     <row r="26">
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>SAÍDAS</t>
-        </is>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>0</v>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>CERTIFICADO DIGITAL - CERTISINGN CERT DIGITAL S 02/2026 06/02/2026 BOLETO 261,72</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>261.72</v>
       </c>
     </row>
     <row r="27">
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>SALDO ATUAL</t>
+      <c r="C27" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0</v>
+        <v>2668.69</v>
       </c>
     </row>
     <row r="28">
       <c r="C28" s="1" t="inlineStr">
         <is>
-          <t>CONTA CORRENTE - FLUXO DE CAIXA DE MANUTENÇÃO</t>
+          <t>(-) CONSERVA��O E MANUTEN��O</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>SALDO ANTERIOR</t>
-        </is>
-      </c>
-      <c r="L29" s="4" t="n">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>- 01/2026 03/02/2026 PIX 371007 71,80</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L30" s="4" t="n">
+        <v>71.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" s="1" t="inlineStr">
+        <is>
+          <t>(-) DISJUNTOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>EXTINTORES - CURITIBA EXTINTORES - EXTINTORES/ MANGUEIRA/ KIT 01/2026 12/02/2026 BOLETO 395 570,67</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>570.67</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="n">
+        <v>570.67</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" s="1" t="inlineStr">
+        <is>
+          <t>(-) LACRES/ TESTE HIDROTATICO/ MANGUEIRA HIDRANTE P3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>MANUTENO - PAULINO VIEIRA DE SOUZA - TROCA DE DJUNTORES 01/2026 03/02/2026 PIX 350,00</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>DESENTUPIMENTO - DESENTUPIDORA DIAMANTE - 11/2025 12/02/2026 BOLETO 6917 682,50</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>682.5</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="n">
+        <v>1032.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" s="1" t="inlineStr">
+        <is>
+          <t>(-) PO�O P.4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>ENTRADAS</t>
-        </is>
-      </c>
-      <c r="L30" s="4" t="n">
-        <v>33637.54</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>SAÍDAS</t>
-        </is>
-      </c>
-      <c r="L31" s="4" t="n">
-        <v>520613.18</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>SALDO ATUAL</t>
-        </is>
-      </c>
-      <c r="L32" s="4" t="n">
+    <row r="40">
+      <c r="C40" s="1" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS ADMINISTRATIVAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>HONORRIOS SNDICO (A) - ROSALDO SANTOS PEREIRA 01/2026 03/02/2026 PIX 2.431,50</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>2431.5</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>HONORRIOS ADMINISTRATIVOS - EG CONDOMNIO 01/2026 03/02/2026TRANSFERNCIA 104 1.189,10</t>
+        </is>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>1189.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>DESPESAS COM CARTRIO - 3 OFICIO REGISTRO DE TITULOS E DOC 12/2025 12/02/2026TRANSFERNCIA 128,33</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>128.33</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="n">
+        <v>3748.93</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" s="1" t="inlineStr">
+        <is>
+          <t>(-) - ATA/ SELO</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>DESP. LEGAIS / MAT. EXPEDIENTE - EG CONDOMNIO - 01/2026 03/02/2026TRANSFERNCIA 50,00</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" s="1" t="inlineStr">
+        <is>
+          <t>(-) BALANCETE - MONTAGEM/ENCADERNA��O</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>DESP. LEGAIS / MAT. EXPEDIENTE - INFOCOPY - XEROX E 01/2026 03/02/2026TRANSFERNCIA 1,50</t>
+        </is>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" s="1" t="inlineStr">
+        <is>
+          <t>(-) IMPRESS�O</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>DESLOCAMENTO - EG CONDOMNIO - DESLOCAMENTO CARTRIO 12/2025 12/02/2026TRANSFERNCIA 24,00</t>
+        </is>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" s="1" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS COM OBRAS E BENFEITORIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>OBRAS E BENFEITORIAS - TSUTSUMI E DE SOUZA - SERVIOS DE 02/2026 10/02/2026 BOLETO 17 2.317,77</t>
+        </is>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>2317.77</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="n">
+        <v>2317.77</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" s="1" t="inlineStr">
+        <is>
+          <t>(-) PINTURA P.12/23</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" s="1" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS POR CONSUMO</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>GS - VANESSA G. PAIVA DIST. GS - BOTIJES ENVASADO 45 01/2026 19/02/2026 BOLETO 24051 900,00</t>
+        </is>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" s="1" t="inlineStr">
+        <is>
+          <t>(-) KGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>ENERGIA - COPEL - UN. CONS. 969273 CONS 750 KWH 01/2026 18/02/2026 DBITO AUT. 731,22</t>
+        </is>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>731.22</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>GUA - SANEPAR - TAMPO (0001.3846) CONS. 273 M 01/2026 18/02/2026 DBITO AUT. 3.612,50</t>
+        </is>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>3612.5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="n">
+        <v>4343.72</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" s="1" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS N�O RATEADAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>BOMBAS - MASSAO BOMBAS - ROLAMENTO/ SELO MECNICO/ 02/2026 06/02/2026 BOLETO 26976/132 612,00</t>
+        </is>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="n">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" s="1" t="inlineStr">
+        <is>
+          <t>(-) RECUPERA��O DE BOMBA CENTRIFUGA PARA �GUA - P. 2/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" s="1" t="inlineStr">
+        <is>
+          <t>(-) CONTRATOS FIXOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>ELEVADORES - ATOSS ELEVADORES - MANUTENO 01/2026 12/02/2026 BOLETO 92 402,21</t>
+        </is>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>402.21</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>ELEVADORES - ATOSS ELEVADORES - PCC 01/2026 19/02/2026 GUIA 92 19,61</t>
+        </is>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>19.61</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="n">
+        <v>421.82</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" s="1" t="inlineStr">
+        <is>
+          <t>(-) DESPESAS BANC�RIAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>DESPESAS BANCRIAS - SICREDI - CESTA DE 02/2026 18/02/2026 DBITO AUT. 19,50</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="n">
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" s="1" t="inlineStr">
+        <is>
+          <t>(-) RELACIONAMENTO</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>DESPESAS BANCRIAS - SICREDI - IRRF 02/2026 27/02/2026 DBITO AUT. 14,11</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>14.11</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>DESPESAS BANCRIAS - SICREDI - IRRF 02/2026 27/02/2026 DBITO AUT. 9,58</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>9.58</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="n">
+        <v>23.69</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL RECEITAS DO MÊS</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="n">
+        <v>16818.77</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL DESPESAS DO MÊS</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="n">
+        <v>16806.59</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" s="1" t="inlineStr">
+        <is>
+          <t>RESUMO DO MÊS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>RECEITAS</t>
+        </is>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>16818.77</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>DESPESAS</t>
+        </is>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>16806.59</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" s="1" t="inlineStr">
+        <is>
+          <t>TOTAL (RECEITAS - DESPESAS)</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="n">
+        <v>12.18</v>
       </c>
     </row>
   </sheetData>
